--- a/data/trans_orig/IP16B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B01-Clase-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>33159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105009</t>
+          <t>104694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>240301</t>
+          <t>239627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47866</t>
+          <t>47701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56173</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68341</t>
+          <t>68750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>80821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>81356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89553</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154721</t>
+          <t>154701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168933</t>
+          <t>168992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63785</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>49574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58533</t>
+          <t>58101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105470</t>
+          <t>105799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119783</t>
+          <t>119778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
